--- a/OUTIL_HSE.xlsx
+++ b/OUTIL_HSE.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{377888C9-F4F4-49B4-93CA-BAB346769ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31C40B59-4EE0-4E69-A66D-29755EEFDEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="YkbxST6YQHHsYE89z2w2QGfUuevtMNgN+Fm7liWsmsBOIdG75/xKGZpNDvCis/krn/UUF0xYF7Up3/NYv0ROgg==" workbookSaltValue="PMU1GnZe4W+sdqdNDvHUnw==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="3" xr2:uid="{002E0343-D81B-440D-A57C-32A2DB09C2FD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{002E0343-D81B-440D-A57C-32A2DB09C2FD}"/>
   </bookViews>
   <sheets>
     <sheet name="GUIDE" sheetId="1" r:id="rId1"/>
@@ -6910,6 +6910,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="3nN5G8gbz1M63VZ0PUAV3QGwC/4zyCYMAgTh31HFK63QHAGoHkdhkIuifPArTs/9N5NEg1U4xuu3JtwVUHY0AA==" saltValue="Z+ddZOdvKt8UuR8JTiuQ/Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
